--- a/excel_db/fee_types.xlsx
+++ b/excel_db/fee_types.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>id</t>
   </si>
@@ -32,6 +32,18 @@
   </si>
   <si>
     <t>created_at</t>
+  </si>
+  <si>
+    <t>description</t>
+  </si>
+  <si>
+    <t>PTA</t>
+  </si>
+  <si>
+    <t>2025-2026</t>
+  </si>
+  <si>
+    <t>2026-06-07 00:10:08</t>
   </si>
 </sst>
 </file>
@@ -389,10 +401,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -410,6 +422,29 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>300</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
